--- a/data/output/librerias_con_info_google.xlsx
+++ b/data/output/librerias_con_info_google.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Mariano Calvache E18-94 y, Quito 170516, Ecuador</t>
+          <t>FLOREANA S/N Y CUCUVE, PUERTO AYORA, SANTA CRUZ, GALAPAGOS, Ecuador</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/?q=place_id:ChIJYQT7unia1ZERm6hXR13euwk</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=FLOREANA%20S/N%20Y%20CUCUVE%2BPUERTO%20AYORA%2BSANTA%20CRUZ%2BGALAPAGOS%2BEcuador</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Tomás De Berlanga, Puerto Ayora 200102, Ecuador</t>
+          <t>FLOREANA S/N Y CUCUVE, PUERTO AYORA, SANTA CRUZ, GALAPAGOS, Ecuador</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/?q=place_id:ChIJL6g5SLtdqpoRXhiHJV1Drzg</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=FLOREANA%20S/N%20Y%20CUCUVE%2BPUERTO%20AYORA%2BSANTA%20CRUZ%2BGALAPAGOS%2BEcuador</t>
         </is>
       </c>
       <c r="X7" t="n">
